--- a/forms/app/assessment_visit.xlsx
+++ b/forms/app/assessment_visit.xlsx
@@ -419,63 +419,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>hint</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>constraint_message</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>instance::type</t>
         </is>
       </c>
     </row>
@@ -492,11 +497,9 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Participant</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -507,10 +510,6 @@
           <t>./source = 'user'</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,15 +522,11 @@
           <t>source</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,15 +539,11 @@
           <t>source_id</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,21 +558,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -594,15 +578,11 @@
           <t>contact_id</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -615,15 +595,11 @@
           <t>name</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,16 +607,6 @@
           <t>end group</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,18 +624,11 @@
           <t>Participant</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -687,18 +646,11 @@
           <t>Select participant</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>select-contact type-participant</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -711,15 +663,11 @@
           <t>patient_id</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -732,15 +680,11 @@
           <t>name</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -753,15 +697,11 @@
           <t>age</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -774,15 +714,11 @@
           <t>gender</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -795,15 +731,11 @@
           <t>phone</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -816,15 +748,11 @@
           <t>education_level</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -834,94 +762,72 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>informant_name</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>cr_no</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>informant_phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>cr_no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>patient_id</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>../inputs/contact/patient_id</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>patient_name</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>../inputs/contact/name</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -931,22 +837,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>patient_uuid</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>patient_sex</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>../inputs/contact/_id</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>../inputs/contact/gender</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -956,22 +859,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>patient_id</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>patient_age</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>../inputs/contact/patient_id</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>../inputs/contact/age</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -981,22 +881,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>patient_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>patient_phone</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>../inputs/contact/name</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>../inputs/contact/phone</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1006,22 +903,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>patient_sex</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>patient_education</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>../inputs/contact/gender</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>../inputs/contact/education_level</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1031,22 +925,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>patient_age</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>patient_cr_no</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>../inputs/contact/age</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>../inputs/contact/cr_no</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1056,122 +947,92 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>patient_phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>screened_by_name</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>../inputs/contact/phone</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>../inputs/user/name</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>patient_education</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>../inputs/contact/education_level</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>g_patient</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>patient_cr_no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>../inputs/contact/cr_no</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>patient_name_confirm</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Patient Name</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>screened_by</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>../inputs/user/contact_id</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>patient_cr_confirm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CR (Case Record) No.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>screened_by_name</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>../inputs/user/name</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1181,405 +1042,339 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>g_assessment</t>
+          <t>g_consent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>Consent</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dateTime</t>
+          <t>select_one consent_mode_list</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>assessment_datetime</t>
+          <t>consent_mode</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Date &amp; time of assessment</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Type of consent obtained</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>now()</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>administered_by</t>
+          <t>consent_given</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Administered by (staff name/s)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>Consent given for screening and data storage?</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Explain purpose, confidentiality and the right to stop at any time.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>begin repeat</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>g_scale</t>
+          <t>consent_recorded_at</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Assessment scales used (record each separately)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>scale_name</t>
+          <t>consent_version</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Assessment scale used</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>NO_LABEL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>'SATORU-CONSENT-v1.0-2026'</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>begin repeat</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>consent_docs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Score / result</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>Consent form / document (upload)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Upload the signed consent form or document. Add more than one if needed.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>interpretation</t>
+          <t>consent_image</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Upload consent form / document (image)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Upload clear photo of consent form. Accepts JPG, JPEG, PNG.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>end repeat</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>consent_pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Upload consent form / document (PDF)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Upload PDF of consent form. Accepts PDF.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>end repeat</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>g_clinical</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Clinical impression</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>clinical_impression</t>
+          <t>g_informant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Provisional diagnosis (post-assessment) / Clinical impression</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+          <t>Informant</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>informant_name</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Respondent name &amp; relation</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>g_followup</t>
+          <t>informant_phone</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Follow-up &amp; notes</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>Informant phone number</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Please enter a valid phone number.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>next_visit_date</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Follow-up / next visit date</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>g_assessment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>Assessment</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>multiline</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>dateTime</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>assessed_by</t>
+          <t>assessment_datetime</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Assessed by (staff - name &amp; signature)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>Date &amp; time of assessment</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1589,93 +1384,85 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>reviewed_by</t>
+          <t>administered_by</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reviewed by (staff - name &amp; signature)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>Administered by (staff name/s)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>begin repeat</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>g_scale</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Assessment scales used (record each separately)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>g_office</t>
+          <t>scale_name</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>For office use only (not part of clinical assessment)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>Assessment scale used</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>entered_in_cht</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Entered in Kobo / CHT</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>Score / result</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1685,89 +1472,633 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qc_checked_by</t>
+          <t>interpretation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Quality control - checked by (name)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>record_id</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Participant kobo / Record ID</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+          <t>end repeat</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>qc_check_date</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Quality control checking date</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>g_clinical</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Clinical impression</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>clinical_impression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Provisional diagnosis (post-assessment) / Clinical impression</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>end group</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>g_followup</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Follow-up &amp; notes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>next_visit_date</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Follow-up / next visit date</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Type your notes here, or upload a notes image below.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>begin repeat</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>notes_docs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Notes upload</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Upload a notes image/document. Add more than one if needed.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>notes_image</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Upload notes image</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Upload clear photo of notes. Accepts JPG, JPEG, PNG.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>notes_pdf</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Upload notes document (PDF)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Upload PDF of notes. Accepts PDF.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>end repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>assessed_by</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Assessed by (staff - name &amp; signature)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>reviewed_by</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Reviewed by (staff - name &amp; signature)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>g_office</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>For office use only (not part of clinical assessment)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>select_one yes_no</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>entered_in_cht</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Entered in Kobo / CHT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>qc_checked_by</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Quality control - checked by (name)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Participant kobo / Record ID</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>qc_check_date</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Quality control checking date</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>g_assessment_sheets</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Assessment sheet</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>begin repeat</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>assessment_sheets</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Assessment sheet upload</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Upload the completed assessment sheet (image or PDF). Add more than one if needed.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>assessment_image</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Upload assessment sheet (image)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Upload clear photo of assessment sheet. Accepts JPG, JPEG, PNG.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>assessment_pdf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Upload assessment sheet (PDF)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Upload PDF of assessment sheet. Accepts PDF.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>end repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>g_supporting_docs</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Supporting Documents / Scale Upload</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>upload_scale_image</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Upload completed scale / assessment sheet (image)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Upload clear photos of the completed paper scale, consent form, or supporting assessment document. Accepts JPG, JPEG, PNG. For PDF use next field.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>upload_scale_pdf</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Upload completed scale / assessment sheet (PDF)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Upload a PDF of the completed paper scale if not already uploaded as image. Accepts PDF.</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>upload_caption</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Attachment caption / description (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1780,21 +2111,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
@@ -1831,6 +2162,40 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>consent_mode_list</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>written</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Written</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>consent_mode_list</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>verbal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Verbal</t>
         </is>
       </c>
     </row>
@@ -1883,7 +2248,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-12 00-00</t>
+          <t>2026-08-20 02-00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
